--- a/output/combinations_stratified.xlsx
+++ b/output/combinations_stratified.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,17 +404,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ampicillin</t>
+          <t>Ampicillin + Gentamicin</t>
         </is>
       </c>
       <c r="C2">
-        <v>0.4139462940361887</v>
+        <v>0.8110873191295113</v>
       </c>
       <c r="D2">
-        <v>0.3314835621350308</v>
+        <v>0.7292531318168372</v>
       </c>
       <c r="E2">
-        <v>0.4872746445357576</v>
+        <v>0.8648109759886096</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -423,7 +423,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -434,17 +434,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ampicillin + Gentamicin</t>
+          <t>Piperacillin/tazobactam + Amikacin</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.8165615249284895</v>
+        <v>0.9167351901221013</v>
       </c>
       <c r="D3">
-        <v>0.7572034233926535</v>
+        <v>0.8531737659889397</v>
       </c>
       <c r="E3">
-        <v>0.8755138333777415</v>
+        <v>0.9587958943848867</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -453,7 +453,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
@@ -464,17 +464,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Piperacillin/tazobactam</t>
+          <t>Vancomycin + Meropenem</t>
         </is>
       </c>
       <c r="C4">
-        <v>0.6983233614908868</v>
+        <v>0.9234478416429089</v>
       </c>
       <c r="D4">
-        <v>0.623294120642931</v>
+        <v>0.8739036136759869</v>
       </c>
       <c r="E4">
-        <v>0.786064319306778</v>
+        <v>0.9599807326252412</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -483,7 +483,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>73</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -494,17 +494,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piperacillin/tazobactam + Amikacin</t>
+          <t>Meropenem</t>
         </is>
       </c>
       <c r="C5">
-        <v>0.9152171193742938</v>
+        <v>0.8477635629580932</v>
       </c>
       <c r="D5">
-        <v>0.8596027557811131</v>
+        <v>0.7842853014137666</v>
       </c>
       <c r="E5">
-        <v>0.9587651708308972</v>
+        <v>0.9045304533947975</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -513,28 +513,28 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EONS</t>
+          <t>HAI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vancomycin</t>
+          <t>Ampicillin + Gentamicin</t>
         </is>
       </c>
       <c r="C6">
-        <v>0.8984162062108494</v>
+        <v>0.7355529759915216</v>
       </c>
       <c r="D6">
-        <v>0.8392924481840554</v>
+        <v>0.6551407043584995</v>
       </c>
       <c r="E6">
-        <v>0.9438051461422683</v>
+        <v>0.799641946590919</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -543,28 +543,28 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EONS</t>
+          <t>HAI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vancomycin + Meropenem</t>
+          <t>Piperacillin/tazobactam + Amikacin</t>
         </is>
       </c>
       <c r="C7">
-        <v>0.9236360402617387</v>
+        <v>0.8967248067806379</v>
       </c>
       <c r="D7">
-        <v>0.8705164105847305</v>
+        <v>0.8302247140316419</v>
       </c>
       <c r="E7">
-        <v>0.9646547417995746</v>
+        <v>0.9325420906346142</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -573,7 +573,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -584,17 +584,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ampicillin</t>
+          <t>Vancomycin + Meropenem</t>
         </is>
       </c>
       <c r="C8">
-        <v>0.2326895148308993</v>
+        <v>0.9296784979302167</v>
       </c>
       <c r="D8">
-        <v>0.1698454251799387</v>
+        <v>0.8849437529327536</v>
       </c>
       <c r="E8">
-        <v>0.305365201929591</v>
+        <v>0.9706399279326776</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -603,7 +603,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -614,17 +614,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ampicillin + Gentamicin</t>
+          <t>Meropenem</t>
         </is>
       </c>
       <c r="C9">
-        <v>0.7372598479155885</v>
+        <v>0.8628159986238924</v>
       </c>
       <c r="D9">
-        <v>0.6523393132689943</v>
+        <v>0.7942112109680494</v>
       </c>
       <c r="E9">
-        <v>0.8073695680792108</v>
+        <v>0.9172951079262901</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -633,127 +633,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HAI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Piperacillin/tazobactam</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.6715352019125697</v>
-      </c>
-      <c r="D10">
-        <v>0.5927579799109917</v>
-      </c>
-      <c r="E10">
-        <v>0.7597653877219712</v>
-      </c>
-      <c r="F10">
-        <v>100</v>
-      </c>
-      <c r="G10">
-        <v>100</v>
-      </c>
-      <c r="H10">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HAI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Piperacillin/tazobactam + Amikacin</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>0.8950351207633265</v>
-      </c>
-      <c r="D11">
-        <v>0.8153874823866689</v>
-      </c>
-      <c r="E11">
-        <v>0.9376461502410414</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>100</v>
-      </c>
-      <c r="H11">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HAI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Vancomycin</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>0.8790075162919901</v>
-      </c>
-      <c r="D12">
-        <v>0.8276493548078805</v>
-      </c>
-      <c r="E12">
-        <v>0.934798932444726</v>
-      </c>
-      <c r="F12">
-        <v>100</v>
-      </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
-      <c r="H12">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HAI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Vancomycin + Meropenem</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0.9297883532754991</v>
-      </c>
-      <c r="D13">
-        <v>0.8749595847770886</v>
-      </c>
-      <c r="E13">
-        <v>0.9665900150725075</v>
-      </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
-      <c r="H13">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
